--- a/assets/DCS_Pattern.xlsx
+++ b/assets/DCS_Pattern.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wesley\Documents\WebOrderAI\weborder-ai\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD970593-19BC-41C9-B0B0-3532A9A5B022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0852FFD-7292-4CF2-B689-C6EE9E24FC2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{3ADF0970-51AE-460E-9CC1-C99EA7AA7C11}"/>
   </bookViews>

--- a/assets/DCS_Pattern.xlsx
+++ b/assets/DCS_Pattern.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wesley\Documents\WebOrderAI\weborder-ai\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0852FFD-7292-4CF2-B689-C6EE9E24FC2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FCBE76A-C79C-4081-A3D2-29BD357B2122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{3ADF0970-51AE-460E-9CC1-C99EA7AA7C11}"/>
   </bookViews>

--- a/assets/DCS_Pattern.xlsx
+++ b/assets/DCS_Pattern.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wesley\Documents\WebOrderAI\weborder-ai\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FCBE76A-C79C-4081-A3D2-29BD357B2122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B8A7ADA-49E2-409B-9BA1-A1668A229DAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{3ADF0970-51AE-460E-9CC1-C99EA7AA7C11}"/>
   </bookViews>
